--- a/docs/Shunt Resistor Quick Start Calculator_v1.1.xlsx
+++ b/docs/Shunt Resistor Quick Start Calculator_v1.1.xlsx
@@ -1,28 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kok/CLionProjects/stm32-digital-potentiometer-v2/docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4671788-A968-4744-9318-3D53044AA586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="DADE" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="555" windowWidth="11400" windowHeight="7425"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShuntCalc" sheetId="1" r:id="rId1"/>
     <sheet name="Rs" sheetId="4" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Jocelyn Chang</author>
     <author>Dean, Christopher</author>
   </authors>
   <commentList>
-    <comment ref="N2" authorId="0">
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -113,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="1">
+    <comment ref="K12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -127,7 +146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M12" authorId="1">
+    <comment ref="M12" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -141,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A16" authorId="1">
+    <comment ref="A16" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -154,7 +173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F19" authorId="1">
+    <comment ref="F19" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -171,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G21" authorId="1">
+    <comment ref="G21" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -184,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G22" authorId="1">
+    <comment ref="G22" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -197,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F28" authorId="1">
+    <comment ref="F28" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -230,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F29" authorId="1">
+    <comment ref="F29" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -243,7 +262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="1">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F31" authorId="1">
+    <comment ref="F31" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -1285,18 +1304,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="##0.00E+0"/>
     <numFmt numFmtId="165" formatCode="##0.000E+0"/>
     <numFmt numFmtId="166" formatCode="##0E+0"/>
     <numFmt numFmtId="167" formatCode="##0.0000E+0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2215,10 +2241,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2226,45 +2252,39 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
@@ -2274,62 +2294,57 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="48" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="48" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="48" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2340,23 +2355,20 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2365,7 +2377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2374,14 +2386,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="48" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="48" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="48" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2390,242 +2399,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2636,39 +2462,222 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2678,12 +2687,29 @@
   </cellStyles>
   <dxfs count="20">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
-        <color theme="9" tint="-0.499984740745262"/>
+        <color rgb="FFC00000"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFB871"/>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2716,28 +2742,11 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
+        <color theme="5" tint="0.59996337778862885"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2770,25 +2779,23 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFC00000"/>
+        <color theme="5" tint="0.59996337778862885"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
+        <color theme="5" tint="0.59996337778862885"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2821,6 +2828,33 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFB871"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FFFF0000"/>
       </font>
@@ -2832,33 +2866,8 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="5" tint="0.59996337778862885"/>
+        <color rgb="FFFF0000"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5" tint="0.59996337778862885"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="5" tint="0.59996337778862885"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2872,6 +2881,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2894,7 +2906,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="Straight Arrow Connector 9"/>
+        <xdr:cNvPr id="10" name="Straight Arrow Connector 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -2941,7 +2959,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="Straight Arrow Connector 10"/>
+        <xdr:cNvPr id="11" name="Straight Arrow Connector 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -2988,7 +3012,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="Straight Arrow Connector 11"/>
+        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -3035,7 +3065,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="TI Logo"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="TI Logo">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -3088,13 +3124,19 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4" name="Group 3"/>
+        <xdr:cNvPr id="4" name="Group 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="10583" y="5881159"/>
-          <a:ext cx="4819650" cy="704078"/>
+          <a:off x="10583" y="5871634"/>
+          <a:ext cx="5499100" cy="707253"/>
           <a:chOff x="9048750" y="2243668"/>
           <a:chExt cx="4561415" cy="489236"/>
         </a:xfrm>
@@ -3103,7 +3145,13 @@
         <mc:Choice Requires="a14">
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="2" name="TextBox 1"/>
+              <xdr:cNvPr id="2" name="TextBox 1">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
               <xdr:cNvSpPr txBox="1"/>
             </xdr:nvSpPr>
             <xdr:spPr>
@@ -3151,7 +3199,7 @@
                                 <a:schemeClr val="tx1"/>
                               </a:solidFill>
                               <a:effectLst/>
-                              <a:latin typeface="Cambria Math"/>
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:cs typeface="+mn-cs"/>
                             </a:rPr>
@@ -3239,7 +3287,7 @@
                                 <a:schemeClr val="tx1"/>
                               </a:solidFill>
                               <a:effectLst/>
-                              <a:latin typeface="Cambria Math"/>
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:cs typeface="+mn-cs"/>
                             </a:rPr>
@@ -3254,7 +3302,7 @@
                                     <a:schemeClr val="tx1"/>
                                   </a:solidFill>
                                   <a:effectLst/>
-                                  <a:latin typeface="Cambria Math"/>
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
@@ -3342,7 +3390,7 @@
                                     <a:schemeClr val="tx1"/>
                                   </a:solidFill>
                                   <a:effectLst/>
-                                  <a:latin typeface="Cambria Math"/>
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
@@ -3393,7 +3441,7 @@
                                     <a:schemeClr val="tx1"/>
                                   </a:solidFill>
                                   <a:effectLst/>
-                                  <a:latin typeface="Cambria Math"/>
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
@@ -3481,7 +3529,7 @@
                                     <a:schemeClr val="tx1"/>
                                   </a:solidFill>
                                   <a:effectLst/>
-                                  <a:latin typeface="Cambria Math"/>
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
@@ -3623,7 +3671,13 @@
         <mc:Choice Requires="a14">
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="14" name="TextBox 13"/>
+              <xdr:cNvPr id="14" name="TextBox 13">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
               <xdr:cNvSpPr txBox="1"/>
             </xdr:nvSpPr>
             <xdr:spPr>
@@ -3671,7 +3725,7 @@
                                 <a:schemeClr val="tx1"/>
                               </a:solidFill>
                               <a:effectLst/>
-                              <a:latin typeface="Cambria Math"/>
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:cs typeface="+mn-cs"/>
                             </a:rPr>
@@ -3759,7 +3813,7 @@
                                 <a:schemeClr val="tx1"/>
                               </a:solidFill>
                               <a:effectLst/>
-                              <a:latin typeface="Cambria Math"/>
+                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               <a:cs typeface="+mn-cs"/>
                             </a:rPr>
@@ -3774,7 +3828,7 @@
                                     <a:schemeClr val="tx1"/>
                                   </a:solidFill>
                                   <a:effectLst/>
-                                  <a:latin typeface="Cambria Math"/>
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
@@ -3862,7 +3916,7 @@
                                     <a:schemeClr val="tx1"/>
                                   </a:solidFill>
                                   <a:effectLst/>
-                                  <a:latin typeface="Cambria Math"/>
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
@@ -3913,7 +3967,7 @@
                                     <a:schemeClr val="tx1"/>
                                   </a:solidFill>
                                   <a:effectLst/>
-                                  <a:latin typeface="Cambria Math"/>
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
@@ -4001,7 +4055,7 @@
                                     <a:schemeClr val="tx1"/>
                                   </a:solidFill>
                                   <a:effectLst/>
-                                  <a:latin typeface="Cambria Math"/>
+                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
@@ -4157,7 +4211,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17"/>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -4201,9 +4261,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4241,7 +4301,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4313,7 +4373,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4486,67 +4546,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:T43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="2.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" customWidth="1"/>
+    <col min="5" max="5" width="2.5" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="15" width="9.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" customWidth="1"/>
+    <col min="16" max="16" width="10.5" customWidth="1"/>
     <col min="17" max="17" width="12" hidden="1" customWidth="1"/>
-    <col min="18" max="19" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="9.140625" customWidth="1"/>
+    <col min="18" max="19" width="9.1640625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="124" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="45"/>
-    </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="126"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="48" t="s">
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="40"/>
+    </row>
+    <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="157"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="43" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -4559,210 +4619,202 @@
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
-      <c r="N3" s="19"/>
-    </row>
-    <row r="4" spans="1:20" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="81" t="s">
+      <c r="N3" s="15"/>
+    </row>
+    <row r="4" spans="1:20" ht="23.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="83"/>
+      <c r="B4" s="104"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="105"/>
       <c r="E4" s="12"/>
-      <c r="F4" s="81" t="str">
+      <c r="F4" s="103" t="str">
         <f>"1) Rs Quick Start " &amp;  R24</f>
         <v xml:space="preserve">1) Rs Quick Start </v>
       </c>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="83"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="98" t="s">
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="105"/>
+    </row>
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="121" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="168"/>
-      <c r="J5" s="169" t="s">
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="170"/>
-      <c r="L5" s="32" t="s">
+      <c r="K5" s="99"/>
+      <c r="L5" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="34"/>
-      <c r="N5" s="35"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="95"/>
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="142" t="s">
+      <c r="M5" s="30"/>
+      <c r="N5" s="31"/>
+    </row>
+    <row r="6" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="118"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="143"/>
-      <c r="I6" s="144"/>
-      <c r="J6" s="29">
+      <c r="H6" s="125"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="25">
         <v>2.5</v>
       </c>
-      <c r="K6" s="80"/>
-      <c r="L6" s="50" t="s">
+      <c r="K6" s="71"/>
+      <c r="L6" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="19"/>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="95"/>
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="32" t="s">
+      <c r="N6" s="15"/>
+    </row>
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="118"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="18"/>
+      <c r="J7" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="K7" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="L7" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="19"/>
-      <c r="R7" s="73"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="95"/>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="129" t="s">
+      <c r="N7" s="15"/>
+      <c r="R7" s="65"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="118"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="162" t="s">
         <v>0</v>
       </c>
-      <c r="H8" s="129"/>
-      <c r="I8" s="129"/>
-      <c r="J8" s="165">
+      <c r="H8" s="162"/>
+      <c r="I8" s="162"/>
+      <c r="J8" s="95">
         <v>3</v>
       </c>
-      <c r="K8" s="165">
-        <v>5.5</v>
-      </c>
-      <c r="L8" s="50" t="s">
+      <c r="K8" s="95">
+        <v>3.3</v>
+      </c>
+      <c r="L8" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="19"/>
-      <c r="R8" s="73"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="95"/>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="129" t="s">
+      <c r="N8" s="15"/>
+      <c r="R8" s="65"/>
+    </row>
+    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="162" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="129"/>
-      <c r="I9" s="129"/>
-      <c r="J9" s="37">
+      <c r="H9" s="162"/>
+      <c r="I9" s="162"/>
+      <c r="J9" s="33">
         <v>1E-3</v>
       </c>
-      <c r="K9" s="37">
+      <c r="K9" s="33">
         <v>2E-3</v>
       </c>
-      <c r="L9" s="50" t="s">
+      <c r="L9" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="M9" s="30"/>
-      <c r="N9" s="31"/>
-    </row>
-    <row r="10" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="95"/>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="129" t="s">
+      <c r="M9" s="26"/>
+      <c r="N9" s="27"/>
+    </row>
+    <row r="10" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="162" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="129"/>
-      <c r="I10" s="129"/>
-      <c r="J10" s="37">
+      <c r="H10" s="162"/>
+      <c r="I10" s="162"/>
+      <c r="J10" s="33">
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="K10" s="37">
+      <c r="K10" s="33">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="L10" s="50" t="s">
+      <c r="L10" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="30"/>
-      <c r="N10" s="31"/>
-      <c r="R10" s="73"/>
-      <c r="T10" s="73"/>
-    </row>
-    <row r="11" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="31"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="92" t="s">
+      <c r="M10" s="26"/>
+      <c r="N10" s="27"/>
+      <c r="R10" s="65"/>
+      <c r="T10" s="65"/>
+    </row>
+    <row r="11" spans="1:20" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="18"/>
+      <c r="H11" s="113"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="47"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="27"/>
+    </row>
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="91"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="18"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="114"/>
       <c r="J12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="87" t="s">
+      <c r="K12" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="88"/>
-      <c r="M12" s="87" t="s">
+      <c r="L12" s="110"/>
+      <c r="M12" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="N12" s="171"/>
+      <c r="N12" s="128"/>
       <c r="Q12" t="s">
         <v>18</v>
       </c>
@@ -4770,73 +4822,72 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="145" t="s">
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="118"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="18"/>
+      <c r="H13" s="169" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="145"/>
+      <c r="I13" s="169"/>
       <c r="J13" s="2" t="str">
         <f>IF(Q13/1000&gt;1,CONCATENATE(TEXT(Q13/1000,"##0.0##")," kΩ"),CONCATENATE(TEXT(Q13,"##0.0")," Ω"))</f>
-        <v>187.5 Ω</v>
-      </c>
-      <c r="K13" s="89" t="str">
+        <v>50.0 Ω</v>
+      </c>
+      <c r="K13" s="111" t="str">
         <f>CONCATENATE(IF(R13/1000&gt;=1,CONCATENATE(TEXT(R13/1000,"###.###")," kΩ"),CONCATENATE(TEXT(R13,"###.0#")," Ω"))," (",R17,")")</f>
-        <v>196.0 Ω (45.9 mW)</v>
-      </c>
-      <c r="L13" s="89"/>
-      <c r="M13" s="101" t="str">
+        <v>51.1 Ω (12.5 mW)</v>
+      </c>
+      <c r="L13" s="111"/>
+      <c r="M13" s="129" t="str">
         <f>CONCATENATE(IF(S13/1000&gt;=1,CONCATENATE(TEXT(S13/1000,"###.###")," kΩ"),CONCATENATE(TEXT(S13,"###.0#")," Ω"))," (",S17,")")</f>
-        <v>200.0 Ω (45.0 mW)</v>
-      </c>
-      <c r="N13" s="172"/>
+        <v>51.0 Ω (12.5 mW)</v>
+      </c>
+      <c r="N13" s="130"/>
       <c r="Q13" s="3">
         <f>(K8-J6)/(J9+K10)</f>
-        <v>187.5</v>
+        <v>49.999999999999986</v>
       </c>
       <c r="R13" s="2">
         <f>INDEX(Rs!D2:D652,MATCH(Q13,Rs!D2:D652,-1))</f>
-        <v>196</v>
+        <v>51.1</v>
       </c>
       <c r="S13" s="2">
         <f>INDEX(Rs!E2:E169,MATCH(Q13,Rs!E2:E169,-1))</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="95" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="96"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="173"/>
-      <c r="G14" s="174"/>
-      <c r="H14" s="175" t="s">
+      <c r="B14" s="119"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="161" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="175"/>
-      <c r="J14" s="176" t="str">
+      <c r="I14" s="161"/>
+      <c r="J14" s="102" t="str">
         <f>IF(Q14/1000&gt;1,CONCATENATE(TEXT(Q14/1000,"###.###")," kΩ"),CONCATENATE(TEXT(Q14,"###.#")," Ω"))</f>
         <v>243.9 Ω</v>
       </c>
-      <c r="K14" s="177" t="str">
+      <c r="K14" s="112" t="str">
         <f>IFERROR(CONCATENATE(IF(R14/1000&gt;=1,CONCATENATE(TEXT(R14/1000,"###.0##")," kΩ"),CONCATENATE(TEXT(R14,"###.0#")," Ω"))," (",R18,")"),"Error")</f>
-        <v>243.0 Ω (37.0 mW)</v>
-      </c>
-      <c r="L14" s="177"/>
-      <c r="M14" s="177" t="str">
+        <v>243.0 Ω (2.6 mW)</v>
+      </c>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112" t="str">
         <f>IFERROR(CONCATENATE(IF(S14/1000&gt;=1,CONCATENATE(TEXT(S14/1000,"##0.0##")," kΩ"),CONCATENATE(TEXT(S14,"##0.0#")," Ω"))," (",S18,")"),"Error")</f>
-        <v>240.0 Ω (37.5 mW)</v>
-      </c>
-      <c r="N14" s="178"/>
+        <v>240.0 Ω (2.7 mW)</v>
+      </c>
+      <c r="N14" s="160"/>
       <c r="Q14" s="4">
         <f>(J8-J6)/(K9+J10)</f>
         <v>243.90243902439022</v>
@@ -4850,223 +4901,214 @@
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="111" t="str">
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="152"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="142" t="str">
         <f>CONCATENATE(Q24,Q25,Q26,Q27,Q28,Q29)</f>
         <v>No Errors</v>
       </c>
-      <c r="G15" s="112"/>
-      <c r="H15" s="112"/>
-      <c r="I15" s="112"/>
-      <c r="J15" s="112"/>
-      <c r="K15" s="112"/>
-      <c r="L15" s="112"/>
-      <c r="M15" s="112"/>
-      <c r="N15" s="113"/>
-      <c r="Q15" s="117" t="s">
+      <c r="G15" s="143"/>
+      <c r="H15" s="143"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="143"/>
+      <c r="K15" s="143"/>
+      <c r="L15" s="143"/>
+      <c r="M15" s="143"/>
+      <c r="N15" s="144"/>
+      <c r="Q15" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="R15" s="74">
+      <c r="R15" s="66">
         <f>($K$8-$J$6)^2/R13</f>
-        <v>4.5918367346938778E-2</v>
-      </c>
-      <c r="S15" s="74">
+        <v>1.2524461839530326E-2</v>
+      </c>
+      <c r="S15" s="66">
         <f>($K$8-$J$6)^2/S13</f>
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="92" t="s">
+        <v>1.2549019607843132E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="93"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="112"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="112"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="112"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="113"/>
-      <c r="Q16" s="117"/>
-      <c r="R16" s="74">
+      <c r="B16" s="116"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
+      <c r="L16" s="143"/>
+      <c r="M16" s="143"/>
+      <c r="N16" s="144"/>
+      <c r="Q16" s="148"/>
+      <c r="R16" s="66">
         <f>($K$8-$J$6)^2/R14</f>
-        <v>3.7037037037037035E-2</v>
-      </c>
-      <c r="S16" s="74">
+        <v>2.6337448559670767E-3</v>
+      </c>
+      <c r="S16" s="66">
         <f>($K$8-$J$6)^2/S14</f>
-        <v>3.7499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="118"/>
-      <c r="B17" s="119"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="115"/>
-      <c r="M17" s="115"/>
-      <c r="N17" s="116"/>
-      <c r="R17" s="75" t="str">
+        <v>2.6666666666666653E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="149"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="151"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="145"/>
+      <c r="G17" s="146"/>
+      <c r="H17" s="146"/>
+      <c r="I17" s="146"/>
+      <c r="J17" s="146"/>
+      <c r="K17" s="146"/>
+      <c r="L17" s="146"/>
+      <c r="M17" s="146"/>
+      <c r="N17" s="147"/>
+      <c r="R17" s="67" t="str">
         <f>IF(R15*1000&gt;=1,CONCATENATE(TEXT(R15*1000,"0.0")," mW"),IF(R15*1000000&gt;=1,CONCATENATE(TEXT(R15*1000000,"0.0")," μW"),CONCATENATE(TEXT(R15,"##0.0#"),"W")))</f>
-        <v>45.9 mW</v>
-      </c>
-      <c r="S17" s="75" t="str">
+        <v>12.5 mW</v>
+      </c>
+      <c r="S17" s="67" t="str">
         <f>IF(S15*1000&gt;=1,CONCATENATE(TEXT(S15*1000,"0.0")," mW"),IF(S15*1000000&gt;=1,CONCATENATE(TEXT(S15*1000000,"0.0")," μW"),CONCATENATE(TEXT(S15,"##0.0#"),"W")))</f>
-        <v>45.0 mW</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="19"/>
-      <c r="R18" s="75" t="str">
+        <v>12.5 mW</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="N18" s="15"/>
+      <c r="R18" s="67" t="str">
         <f>IF(R16*1000&gt;=1,CONCATENATE(TEXT(R16*1000,"0.0")," mW"),IF(R16*1000000&gt;=1,CONCATENATE(TEXT(R16*1000000,"0.0")," μW"),CONCATENATE(TEXT(R16,"##0.0#"),"W")))</f>
-        <v>37.0 mW</v>
-      </c>
-      <c r="S18" s="75" t="str">
+        <v>2.6 mW</v>
+      </c>
+      <c r="S18" s="67" t="str">
         <f>IF(S16*1000&gt;=1,CONCATENATE(TEXT(S16*1000,"0.0")," mW"),IF(S16*1000000&gt;=1,CONCATENATE(TEXT(S16*1000000,"0.0")," μW"),CONCATENATE(TEXT(S16,"##0.0#"),"W")))</f>
-        <v>37.5 mW</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="84" t="s">
+        <v>2.7 mW</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="23.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="82" t="str">
+      <c r="B19" s="107"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="108"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="104" t="str">
         <f>"2) Schematic  Overlay  " &amp; R32</f>
         <v xml:space="preserve">2) Schematic  Overlay  </v>
       </c>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="60"/>
-    </row>
-    <row r="20" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="46" t="s">
+      <c r="H19" s="104"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="104"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="104"/>
+      <c r="N19" s="53"/>
+    </row>
+    <row r="20" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="108" t="s">
+      <c r="B20" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="109"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="62" t="s">
+      <c r="C20" s="138"/>
+      <c r="D20" s="139"/>
+      <c r="F20" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="63" t="s">
+      <c r="G20" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="64" t="s">
+      <c r="H20" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="70"/>
-      <c r="J20" s="150"/>
-      <c r="K20" s="150"/>
-      <c r="L20" s="150"/>
-      <c r="M20" s="150"/>
-      <c r="N20" s="151"/>
-    </row>
-    <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="102" t="s">
+      <c r="I20" s="62"/>
+      <c r="J20" s="82"/>
+      <c r="K20" s="82"/>
+      <c r="L20" s="82"/>
+      <c r="M20" s="82"/>
+      <c r="N20" s="83"/>
+    </row>
+    <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="133" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="104"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="138" t="s">
+      <c r="C21" s="133"/>
+      <c r="D21" s="134"/>
+      <c r="F21" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="48">
         <f>J6</f>
         <v>2.5</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H21" s="54" t="s">
         <v>4</v>
       </c>
       <c r="I21" s="9"/>
-      <c r="J21" s="152"/>
-      <c r="K21" s="153" t="s">
+      <c r="J21" s="84"/>
+      <c r="K21" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="L21" s="154" t="str">
+      <c r="L21" s="86" t="str">
         <f>CONCATENATE(G24," V")</f>
-        <v>3.8 V</v>
-      </c>
-      <c r="M21" s="152"/>
-      <c r="N21" s="155"/>
+        <v>3.3 V</v>
+      </c>
+      <c r="M21" s="84"/>
+      <c r="N21" s="87"/>
       <c r="Q21" t="s">
         <v>21</v>
       </c>
       <c r="R21">
         <f>IFERROR(MATCH(G26,Rs!A2:A652,0),-1)</f>
-        <v>215</v>
+        <v>-1</v>
       </c>
       <c r="S21">
         <f>IFERROR(MATCH(G26,Rs!B2:B652,0),-1)</f>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="103"/>
-      <c r="B22" s="106"/>
-      <c r="C22" s="106"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="140" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="132"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="136"/>
+      <c r="F22" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="49">
         <f>J10</f>
         <v>5.0000000000000002E-5</v>
       </c>
-      <c r="H22" s="66" t="s">
+      <c r="H22" s="58" t="s">
         <v>5</v>
       </c>
       <c r="I22" s="9"/>
-      <c r="J22" s="152"/>
-      <c r="K22" s="152"/>
-      <c r="L22" s="152"/>
-      <c r="M22" s="152"/>
-      <c r="N22" s="155"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="87"/>
       <c r="Q22" t="s">
         <v>20</v>
       </c>
@@ -5075,70 +5117,68 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="130" t="s">
+    <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="132" t="s">
+      <c r="B23" s="165" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="132"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="140" t="s">
+      <c r="C23" s="165"/>
+      <c r="D23" s="166"/>
+      <c r="F23" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="56">
+      <c r="G23" s="49">
         <f>K10</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="H23" s="66" t="s">
+      <c r="H23" s="58" t="s">
         <v>5</v>
       </c>
       <c r="I23" s="9"/>
-      <c r="J23" s="152"/>
-      <c r="K23" s="152"/>
-      <c r="L23" s="152"/>
-      <c r="M23" s="152"/>
-      <c r="N23" s="155"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="87"/>
       <c r="Q23" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="131"/>
-      <c r="B24" s="134"/>
-      <c r="C24" s="134"/>
-      <c r="D24" s="135"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="141" t="s">
+    <row r="24" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="164"/>
+      <c r="B24" s="167"/>
+      <c r="C24" s="167"/>
+      <c r="D24" s="168"/>
+      <c r="F24" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="G24" s="57">
-        <v>3.8</v>
-      </c>
-      <c r="H24" s="67" t="s">
+      <c r="G24" s="50">
+        <v>3.3</v>
+      </c>
+      <c r="H24" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="148" t="s">
+      <c r="I24" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="J24" s="156" t="str">
+      <c r="J24" s="88" t="str">
         <f>CONCATENATE(ROUND(G28*1000,3)," mA")</f>
-        <v>6.19 mA</v>
-      </c>
-      <c r="K24" s="147" t="s">
+        <v>3.636 mA</v>
+      </c>
+      <c r="K24" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="L24" s="157" t="str">
+      <c r="L24" s="89" t="str">
         <f>IF(G26/1000&gt;=1,CONCATENATE(TEXT(G26/1000,"##0.000")," kΩ"),CONCATENATE(TEXT(G26,"##0.0#")," Ω"))</f>
-        <v>210.0 Ω</v>
-      </c>
-      <c r="M24" s="158" t="str">
+        <v>220.0 Ω</v>
+      </c>
+      <c r="M24" s="140" t="str">
         <f>CONCATENATE(TEXT(G30,"0.0##"), " V (",TEXT(G30*G28*1000,"#0.0##")," mW)")</f>
-        <v>1.3 V (8.048 mW)</v>
-      </c>
-      <c r="N24" s="159"/>
+        <v>0.8 V (2.909 mW)</v>
+      </c>
+      <c r="N24" s="141"/>
       <c r="Q24" t="str">
         <f>IF(R22=0,"No Errors","")</f>
         <v>No Errors</v>
@@ -5148,188 +5188,177 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="B25" s="128"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="137" t="s">
+    <row r="25" spans="1:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="B25" s="159"/>
+      <c r="C25" s="159"/>
+      <c r="D25" s="159"/>
+      <c r="F25" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="G25" s="58">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="H25" s="65" t="s">
+      <c r="G25" s="51">
+        <v>2E-3</v>
+      </c>
+      <c r="H25" s="54" t="s">
         <v>5</v>
       </c>
       <c r="I25" s="9"/>
-      <c r="J25" s="152"/>
-      <c r="K25" s="152"/>
-      <c r="L25" s="152"/>
-      <c r="M25" s="152"/>
-      <c r="N25" s="155"/>
-      <c r="Q25" s="36" t="str">
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="87"/>
+      <c r="Q25" s="32" t="str">
         <f>IF(J8&gt;K8,"Error: VINmin &gt; VINmax" &amp; CHAR(10),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="22"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="136" t="s">
+    <row r="26" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="F26" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="166">
-        <v>210</v>
-      </c>
-      <c r="H26" s="65" t="s">
+      <c r="G26" s="96">
+        <v>220</v>
+      </c>
+      <c r="H26" s="54" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="9"/>
-      <c r="J26" s="152"/>
-      <c r="K26" s="152" t="s">
+      <c r="J26" s="84"/>
+      <c r="K26" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="L26" s="146" t="s">
+      <c r="L26" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="M26" s="160" t="str">
+      <c r="M26" s="90" t="str">
         <f>CONCATENATE(G21," V")</f>
         <v>2.5 V</v>
       </c>
-      <c r="N26" s="155"/>
-      <c r="Q26" s="36" t="str">
+      <c r="N26" s="87"/>
+      <c r="Q26" s="32" t="str">
         <f>IF(K9&lt;J9,"Error: I_Load Min &gt; I_Load Max" &amp; CHAR(10),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="81" t="s">
+    <row r="27" spans="1:19" ht="23.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="82"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="68" t="s">
+      <c r="B27" s="104"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="105"/>
+      <c r="F27" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="59"/>
-      <c r="H27" s="69"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="61"/>
       <c r="I27" s="9"/>
-      <c r="J27" s="152"/>
-      <c r="K27" s="152"/>
-      <c r="L27" s="152"/>
-      <c r="M27" s="152"/>
-      <c r="N27" s="155"/>
-      <c r="Q27" s="36" t="str">
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="87"/>
+      <c r="Q27" s="32" t="str">
         <f>IF(K10&lt;J10,"Error: IQ Min&gt; IQ Max" &amp; CHAR(10),"")</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="A28" s="51"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="137" t="s">
+    <row r="28" spans="1:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="A28" s="46"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="31"/>
+      <c r="F28" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="163">
+      <c r="G28" s="93">
         <f>G30/G26</f>
-        <v>6.1904761904761898E-3</v>
-      </c>
-      <c r="H28" s="61" t="s">
+        <v>3.6363636363636355E-3</v>
+      </c>
+      <c r="H28" s="54" t="s">
         <v>5</v>
       </c>
       <c r="I28" s="9"/>
-      <c r="J28" s="152" t="s">
+      <c r="J28" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="K28" s="152"/>
-      <c r="L28" s="148" t="s">
+      <c r="K28" s="84"/>
+      <c r="L28" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="M28" s="161" t="str">
+      <c r="M28" s="91" t="str">
         <f>CONCATENATE(ROUND(G25*1000,4)," mA")</f>
-        <v>2.5 mA</v>
-      </c>
-      <c r="N28" s="155"/>
-      <c r="Q28" s="36" t="str">
+        <v>2 mA</v>
+      </c>
+      <c r="N28" s="87"/>
+      <c r="Q28" s="32" t="str">
         <f>IF(Q13&gt;Q14,"Error: Rs_min &gt; Rs_max. Vin or Load bounds too wide, or VREF &gt;= VINmin" &amp; CHAR(10),"")</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="22"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="138" t="s">
+    <row r="29" spans="1:19" ht="19" x14ac:dyDescent="0.25">
+      <c r="A29" s="18"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="15"/>
+      <c r="F29" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G29" s="164">
+      <c r="G29" s="94">
         <f>IF(G28-G25&gt;0,G28-G25,0)</f>
-        <v>3.6904761904761898E-3</v>
-      </c>
-      <c r="H29" s="61" t="s">
+        <v>1.6363636363636355E-3</v>
+      </c>
+      <c r="H29" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="I29" s="147" t="s">
+      <c r="I29" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="J29" s="149" t="str">
+      <c r="J29" s="81" t="str">
         <f>CONCATENATE(ROUND(G29*1000,3)," mA")</f>
-        <v>3.69 mA</v>
-      </c>
-      <c r="K29" s="152"/>
-      <c r="L29" s="152"/>
-      <c r="M29" s="152"/>
-      <c r="N29" s="155"/>
-      <c r="Q29" s="38" t="str">
+        <v>1.636 mA</v>
+      </c>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="87"/>
+      <c r="Q29" s="32" t="str">
         <f>IF(J6&gt;=J8,"Error: VREF &gt;= VINmin" &amp; CHAR(10),"")</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="24"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="137" t="s">
+    <row r="30" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="20"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="35"/>
+      <c r="F30" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="54">
+      <c r="G30" s="48">
         <f>IF(G24-G21&gt;0,G24-G21,0)</f>
-        <v>1.2999999999999998</v>
-      </c>
-      <c r="H30" s="61" t="s">
+        <v>0.79999999999999982</v>
+      </c>
+      <c r="H30" s="54" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="9"/>
-      <c r="J30" s="162"/>
-      <c r="K30" s="152"/>
-      <c r="L30" s="152"/>
-      <c r="M30" s="152"/>
-      <c r="N30" s="155"/>
-      <c r="Q30" s="38"/>
-    </row>
-    <row r="31" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E31" s="13"/>
-      <c r="F31" s="139" t="s">
+      <c r="J30" s="92"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="87"/>
+      <c r="Q30" s="32"/>
+    </row>
+    <row r="31" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F31" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="G31" s="77">
+      <c r="G31" s="69">
         <f>G28*G30</f>
-        <v>8.0476190476190465E-3</v>
-      </c>
-      <c r="H31" s="76" t="s">
+        <v>2.9090909090909076E-3</v>
+      </c>
+      <c r="H31" s="68" t="s">
         <v>40</v>
       </c>
       <c r="I31" s="9"/>
@@ -5337,7 +5366,7 @@
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="23"/>
+      <c r="N31" s="19"/>
       <c r="Q31" t="s">
         <v>29</v>
       </c>
@@ -5349,26 +5378,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="81" t="s">
+    <row r="32" spans="1:19" ht="20" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="82"/>
-      <c r="C32" s="82"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="111" t="str">
+      <c r="B32" s="104"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="105"/>
+      <c r="F32" s="142" t="str">
         <f>CONCATENATE(Q32,Q33,Q34,Q35,Q36)</f>
         <v>No Errors</v>
       </c>
-      <c r="G32" s="112"/>
-      <c r="H32" s="113"/>
-      <c r="I32" s="71"/>
+      <c r="G32" s="143"/>
+      <c r="H32" s="144"/>
+      <c r="I32" s="63"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
-      <c r="N32" s="23"/>
+      <c r="N32" s="19"/>
       <c r="Q32" t="str">
         <f>IF(AND(S31=0,Q36=""),"No Errors","")</f>
         <v>No Errors</v>
@@ -5378,87 +5406,78 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="39" t="s">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A33" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="111"/>
-      <c r="G33" s="112"/>
-      <c r="H33" s="113"/>
-      <c r="I33" s="71"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
+      <c r="F33" s="142"/>
+      <c r="G33" s="143"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="63"/>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
-      <c r="N33" s="23"/>
-      <c r="Q33" s="38" t="str">
+      <c r="N33" s="19"/>
+      <c r="Q33" s="32" t="str">
         <f>IF(G21&gt;=G24,"Error: VREF &gt;= VINmin" &amp; CHAR(10),"")</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="39" t="s">
+    <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="111"/>
-      <c r="G34" s="112"/>
-      <c r="H34" s="113"/>
-      <c r="I34" s="71"/>
+      <c r="D34" s="15"/>
+      <c r="F34" s="142"/>
+      <c r="G34" s="143"/>
+      <c r="H34" s="144"/>
+      <c r="I34" s="63"/>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
-      <c r="N34" s="23"/>
-      <c r="Q34" s="38" t="str">
+      <c r="N34" s="19"/>
+      <c r="Q34" s="32" t="str">
         <f>IFERROR(IF(G29&lt;J10,"Error: I_Q &lt; I_Qmin.  Try reducing load current or reducing R"&amp;CHAR(10),""),"Error: Calculation Error. Inputs must be strictly numbers, and cannot have units (e.g R: 3.3k is invalid, please use 3300)")</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="41" t="s">
+    <row r="35" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="114"/>
-      <c r="G35" s="115"/>
-      <c r="H35" s="116"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="28"/>
-      <c r="Q35" s="38" t="str">
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="145"/>
+      <c r="G35" s="146"/>
+      <c r="H35" s="147"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="24"/>
+      <c r="Q35" s="32" t="str">
         <f>IFERROR(IF(G29&gt;K10,"Error: IQ &gt; IQmax." &amp;CHAR(10) &amp;"Try increasing R." &amp; CHAR(10),""),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="15"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="Q36" s="167" t="str">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A36" s="14"/>
+      <c r="Q36" s="97" t="str">
         <f>IF(G29=K10,"Warning: IQ calculated equal to IQmax. Consider using a larger resistor to decrease IQ","")</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection password="DADE" sheet="1" objects="1" scenarios="1"/>
   <scenarios current="0" show="0">
@@ -5505,108 +5524,108 @@
     <mergeCell ref="A12:D13"/>
     <mergeCell ref="A5:D11"/>
   </mergeCells>
-  <conditionalFormatting sqref="J9:K9">
-    <cfRule type="expression" dxfId="19" priority="23">
-      <formula>IF(K9&lt;J9,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J10">
-    <cfRule type="expression" dxfId="18" priority="22">
-      <formula>IF(K10&lt;J10,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8">
-    <cfRule type="expression" dxfId="17" priority="21">
-      <formula>IF(K8&lt;J8,TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="F32">
+    <cfRule type="expression" dxfId="19" priority="8">
+      <formula>IF($S$31&lt;&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:G15">
-    <cfRule type="expression" dxfId="16" priority="14">
+    <cfRule type="expression" dxfId="18" priority="14">
       <formula>IF($R$22&gt;0,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+      <formula>$K$10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="52">
+      <formula>OR($G$29&lt;$J$10,$G$29&gt;$K$10)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="53">
+      <formula>AND($G$29&gt;0,$G$29&lt;$K$10)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G30">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="12" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6">
-    <cfRule type="cellIs" dxfId="13" priority="50" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="50" operator="greaterThanOrEqual">
       <formula>$J$8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="expression" dxfId="1" priority="52">
-      <formula>OR($G$29&lt;$J$10,$G$29&gt;$K$10)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="53">
-      <formula>AND($G$29&gt;0,$G$29&lt;$K$10)</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>$K$10</formula>
+  <conditionalFormatting sqref="J8">
+    <cfRule type="expression" dxfId="11" priority="21">
+      <formula>IF(K8&lt;J8,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="expression" dxfId="12" priority="8">
-      <formula>IF($S$31&lt;&gt;0,TRUE,FALSE)</formula>
+  <conditionalFormatting sqref="J10">
+    <cfRule type="expression" dxfId="10" priority="22">
+      <formula>IF(K10&lt;J10,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28 J24">
-    <cfRule type="expression" dxfId="11" priority="58">
+  <conditionalFormatting sqref="J24 G28">
+    <cfRule type="expression" dxfId="9" priority="58">
       <formula>AND($G$28&gt;0,$G$28&lt;$K$10+$G$25)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="59">
+    <cfRule type="expression" dxfId="8" priority="59">
       <formula>OR($G$28&lt;=0,$G$28&gt;$K$10+$G$25)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J29">
+    <cfRule type="expression" dxfId="7" priority="76">
+      <formula>OR(G29&gt;$K$10,G29&lt;$J$10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J9:K9">
+    <cfRule type="expression" dxfId="6" priority="23">
+      <formula>IF(K9&lt;J9,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8">
+    <cfRule type="expression" dxfId="5" priority="2">
+      <formula>IF($K$8&lt;$J$8,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K13:K14">
-    <cfRule type="expression" dxfId="9" priority="72">
+    <cfRule type="expression" dxfId="4" priority="72">
       <formula>$R$14&gt;=$R$13</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="73">
+    <cfRule type="expression" dxfId="3" priority="73">
       <formula>$R$13&gt;$R$14</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M24">
+    <cfRule type="expression" dxfId="2" priority="77">
+      <formula>$G$29&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M13:N14">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$S$13&gt;$S$14</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>$S$14&gt;=$S$13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J29">
-    <cfRule type="expression" dxfId="5" priority="76">
-      <formula>OR(G29&gt;$K$10,G29&lt;$J$10)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M24">
-    <cfRule type="expression" dxfId="4" priority="77">
-      <formula>$G$29&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K8">
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>IF($K$8&lt;$J$8,TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error: Invalid Input" error="Invalid input value. Please enter only numeric values to the input cells._x000a__x000a_For example: 1500 instead of 1.5k, or 15e-3 instead of 15m_x000a__x000a_Click Retry to enter a new value." sqref="J8:K10">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error: Invalid Input" error="Invalid input value. Please enter only numeric values to the input cells._x000a__x000a_For example: 1500 instead of 1.5k, or 15e-3 instead of 15m_x000a__x000a_Click Retry to enter a new value." sqref="J8:K10" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>-999999</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error: Invalid Input" error="Invalid input value. Please enter only numeric values to the input cells._x000a__x000a_For example: 1500 instead of 1.5k, or 15e-3 instead of 15m_x000a__x000a_Click Retry to enter a new value." sqref="G24:G26">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error: Invalid Input" error="Invalid input value. Please enter only numeric values to the input cells._x000a__x000a_For example: 1500 instead of 1.5k, or 15e-3 instead of 15m_x000a__x000a_Click Retry to enter a new value." sqref="G24:G26" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A33" r:id="rId1" display="TI Voltage References"/>
-    <hyperlink ref="A34" r:id="rId2" location="instructions"/>
-    <hyperlink ref="A35" r:id="rId3"/>
+    <hyperlink ref="A33" r:id="rId1" display="TI Voltage References" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A34" r:id="rId2" location="instructions" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A35" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
@@ -5616,18 +5635,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:CV680"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" customWidth="1"/>
+    <col min="1" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>14</v>
       </c>
@@ -5733,7 +5752,7 @@
       <c r="CU1" s="1"/>
       <c r="CV1" s="1"/>
     </row>
-    <row r="2" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5777,7 +5796,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="3" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1.02</v>
       </c>
@@ -5821,7 +5840,7 @@
         <v>1020000</v>
       </c>
     </row>
-    <row r="4" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1.05</v>
       </c>
@@ -5865,7 +5884,7 @@
         <v>1050000</v>
       </c>
     </row>
-    <row r="5" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1.0699999999999998</v>
       </c>
@@ -5909,7 +5928,7 @@
         <v>1070000</v>
       </c>
     </row>
-    <row r="6" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1.1000000000000001</v>
       </c>
@@ -5953,7 +5972,7 @@
         <v>1100000</v>
       </c>
     </row>
-    <row r="7" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1.1300000000000001</v>
       </c>
@@ -5997,7 +6016,7 @@
         <v>1130000</v>
       </c>
     </row>
-    <row r="8" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1.1499999999999999</v>
       </c>
@@ -6041,7 +6060,7 @@
         <v>1150000</v>
       </c>
     </row>
-    <row r="9" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1.1800000000000002</v>
       </c>
@@ -6085,7 +6104,7 @@
         <v>1180000</v>
       </c>
     </row>
-    <row r="10" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1.21</v>
       </c>
@@ -6129,7 +6148,7 @@
         <v>1210000</v>
       </c>
     </row>
-    <row r="11" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1.24</v>
       </c>
@@ -6173,7 +6192,7 @@
         <v>1240000</v>
       </c>
     </row>
-    <row r="12" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1.27</v>
       </c>
@@ -6217,7 +6236,7 @@
         <v>1270000</v>
       </c>
     </row>
-    <row r="13" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1.3</v>
       </c>
@@ -6261,7 +6280,7 @@
         <v>1300000</v>
       </c>
     </row>
-    <row r="14" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1.33</v>
       </c>
@@ -6305,7 +6324,7 @@
         <v>1330000</v>
       </c>
     </row>
-    <row r="15" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1.3699999999999999</v>
       </c>
@@ -6349,7 +6368,7 @@
         <v>1370000</v>
       </c>
     </row>
-    <row r="16" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1.4</v>
       </c>
@@ -6393,7 +6412,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1.4300000000000002</v>
       </c>
@@ -6437,7 +6456,7 @@
         <v>1430000</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1.47</v>
       </c>
@@ -6481,7 +6500,7 @@
         <v>1470000</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1.5</v>
       </c>
@@ -6525,7 +6544,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1.54</v>
       </c>
@@ -6569,7 +6588,7 @@
         <v>1540000</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1.58</v>
       </c>
@@ -6613,7 +6632,7 @@
         <v>1580000</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1.6199999999999999</v>
       </c>
@@ -6657,7 +6676,7 @@
         <v>1620000</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1.65</v>
       </c>
@@ -6701,7 +6720,7 @@
         <v>1650000</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1.69</v>
       </c>
@@ -6745,7 +6764,7 @@
         <v>1690000</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1.7399999999999998</v>
       </c>
@@ -6789,7 +6808,7 @@
         <v>1740000</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1.8199999999999998</v>
       </c>
@@ -6833,7 +6852,7 @@
         <v>1820000</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1.9600000000000002</v>
       </c>
@@ -6877,7 +6896,7 @@
         <v>1960000</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2</v>
       </c>
@@ -6921,7 +6940,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2.0499999999999998</v>
       </c>
@@ -6965,7 +6984,7 @@
         <v>2050000</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2.1</v>
       </c>
@@ -7009,7 +7028,7 @@
         <v>2100000</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2.15</v>
       </c>
@@ -7053,7 +7072,7 @@
         <v>2150000</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2.21</v>
       </c>
@@ -7097,7 +7116,7 @@
         <v>2210000</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2.2600000000000002</v>
       </c>
@@ -7141,7 +7160,7 @@
         <v>2260000</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2.3199999999999998</v>
       </c>
@@ -7185,7 +7204,7 @@
         <v>2320000</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2.37</v>
       </c>
@@ -7229,7 +7248,7 @@
         <v>2370000</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2.4300000000000002</v>
       </c>
@@ -7273,7 +7292,7 @@
         <v>2430000</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2.4899999999999998</v>
       </c>
@@ -7317,7 +7336,7 @@
         <v>2490000</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>2.5499999999999998</v>
       </c>
@@ -7361,7 +7380,7 @@
         <v>2550000</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>2.6100000000000003</v>
       </c>
@@ -7405,7 +7424,7 @@
         <v>2610000</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>2.67</v>
       </c>
@@ -7449,7 +7468,7 @@
         <v>2670000</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>2.7399999999999998</v>
       </c>
@@ -7493,7 +7512,7 @@
         <v>2740000</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>2.8</v>
       </c>
@@ -7537,7 +7556,7 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>2.87</v>
       </c>
@@ -7581,7 +7600,7 @@
         <v>2870000</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>2.94</v>
       </c>
@@ -7625,7 +7644,7 @@
         <v>2940000</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>3.0100000000000002</v>
       </c>
@@ -7669,7 +7688,7 @@
         <v>3010000</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>3.09</v>
       </c>
@@ -7713,7 +7732,7 @@
         <v>3090000</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>3.16</v>
       </c>
@@ -7757,7 +7776,7 @@
         <v>3160000</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>3.2399999999999998</v>
       </c>
@@ -7801,7 +7820,7 @@
         <v>3240000</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3.3200000000000003</v>
       </c>
@@ -7845,7 +7864,7 @@
         <v>3320000</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>3.4</v>
       </c>
@@ -7889,7 +7908,7 @@
         <v>3400000</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>3.4799999999999995</v>
       </c>
@@ -7933,7 +7952,7 @@
         <v>3480000</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>3.5700000000000003</v>
       </c>
@@ -7977,7 +7996,7 @@
         <v>3570000</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>3.65</v>
       </c>
@@ -8021,7 +8040,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>3.7399999999999998</v>
       </c>
@@ -8065,7 +8084,7 @@
         <v>3740000</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>3.8299999999999996</v>
       </c>
@@ -8109,7 +8128,7 @@
         <v>3830000</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>3.9200000000000004</v>
       </c>
@@ -8153,7 +8172,7 @@
         <v>3920000</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>4.0200000000000005</v>
       </c>
@@ -8197,7 +8216,7 @@
         <v>4020000</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>4.12</v>
       </c>
@@ -8241,7 +8260,7 @@
         <v>4120000</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>4.24</v>
       </c>
@@ -8285,7 +8304,7 @@
         <v>4240000</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>4.32</v>
       </c>
@@ -8329,7 +8348,7 @@
         <v>4320000</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4.42</v>
       </c>
@@ -8373,7 +8392,7 @@
         <v>4420000</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>4.5200000000000005</v>
       </c>
@@ -8417,7 +8436,7 @@
         <v>4520000</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>4.6399999999999997</v>
       </c>
@@ -8461,7 +8480,7 @@
         <v>4640000</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>4.75</v>
       </c>
@@ -8505,7 +8524,7 @@
         <v>4750000</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>4.87</v>
       </c>
@@ -8549,7 +8568,7 @@
         <v>4870000</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4.99</v>
       </c>
@@ -8593,7 +8612,7 @@
         <v>4990000</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>5.1100000000000003</v>
       </c>
@@ -8637,7 +8656,7 @@
         <v>5110000</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>5.2299999999999995</v>
       </c>
@@ -8681,7 +8700,7 @@
         <v>5230000</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>5.36</v>
       </c>
@@ -8725,7 +8744,7 @@
         <v>5360000</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5.49</v>
       </c>
@@ -8769,7 +8788,7 @@
         <v>5490000</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>5.62</v>
       </c>
@@ -8813,7 +8832,7 @@
         <v>5620000</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>5.76</v>
       </c>
@@ -8857,7 +8876,7 @@
         <v>5760000</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>5.9</v>
       </c>
@@ -8901,7 +8920,7 @@
         <v>5900000</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>6.04</v>
       </c>
@@ -8945,7 +8964,7 @@
         <v>6040000</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>6.1899999999999995</v>
       </c>
@@ -8989,7 +9008,7 @@
         <v>6190000</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>6.34</v>
       </c>
@@ -9033,7 +9052,7 @@
         <v>6340000</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>6.49</v>
       </c>
@@ -9077,7 +9096,7 @@
         <v>6490000</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>6.65</v>
       </c>
@@ -9121,7 +9140,7 @@
         <v>6650000</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>6.81</v>
       </c>
@@ -9165,7 +9184,7 @@
         <v>6810000</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>6.9799999999999995</v>
       </c>
@@ -9209,7 +9228,7 @@
         <v>6980000</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>7.15</v>
       </c>
@@ -9253,7 +9272,7 @@
         <v>7150000</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>7.32</v>
       </c>
@@ -9297,7 +9316,7 @@
         <v>7320000</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>7.5</v>
       </c>
@@ -9341,7 +9360,7 @@
         <v>7500000</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>7.68</v>
       </c>
@@ -9385,7 +9404,7 @@
         <v>7680000</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>7.87</v>
       </c>
@@ -9429,7 +9448,7 @@
         <v>7870000</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>8.0599999999999987</v>
       </c>
@@ -9473,7 +9492,7 @@
         <v>8060000</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>8.25</v>
       </c>
@@ -9517,7 +9536,7 @@
         <v>8250000</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>8.4499999999999993</v>
       </c>
@@ -9561,7 +9580,7 @@
         <v>8450000</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>8.66</v>
       </c>
@@ -9605,7 +9624,7 @@
         <v>8660000</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>8.870000000000001</v>
       </c>
@@ -9649,7 +9668,7 @@
         <v>8870000</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>9.09</v>
       </c>
@@ -9693,7 +9712,7 @@
         <v>9090000</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>9.3099999999999987</v>
       </c>
@@ -9737,7 +9756,7 @@
         <v>9310000</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>9.5299999999999994</v>
       </c>
@@ -9781,7 +9800,7 @@
         <v>9530000</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>9.76</v>
       </c>
@@ -9825,7 +9844,7 @@
         <v>9760000</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>10</v>
       </c>
@@ -9842,7 +9861,7 @@
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>10.199999999999999</v>
       </c>
@@ -9859,7 +9878,7 @@
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>10.5</v>
       </c>
@@ -9876,7 +9895,7 @@
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>10.7</v>
       </c>
@@ -9893,7 +9912,7 @@
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>11</v>
       </c>
@@ -9910,7 +9929,7 @@
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>11.3</v>
       </c>
@@ -9927,7 +9946,7 @@
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>11.5</v>
       </c>
@@ -9944,7 +9963,7 @@
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>11.8</v>
       </c>
@@ -9961,7 +9980,7 @@
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>12.1</v>
       </c>
@@ -9978,7 +9997,7 @@
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>12.4</v>
       </c>
@@ -9995,7 +10014,7 @@
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>12.7</v>
       </c>
@@ -10012,7 +10031,7 @@
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>13</v>
       </c>
@@ -10029,7 +10048,7 @@
       <c r="G106" s="1"/>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>13.3</v>
       </c>
@@ -10046,7 +10065,7 @@
       <c r="G107" s="1"/>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>13.7</v>
       </c>
@@ -10063,7 +10082,7 @@
       <c r="G108" s="1"/>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>14</v>
       </c>
@@ -10080,7 +10099,7 @@
       <c r="G109" s="1"/>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>14.3</v>
       </c>
@@ -10097,7 +10116,7 @@
       <c r="G110" s="1"/>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>14.7</v>
       </c>
@@ -10114,7 +10133,7 @@
       <c r="G111" s="1"/>
       <c r="H111" s="1"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>15</v>
       </c>
@@ -10131,7 +10150,7 @@
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>15.4</v>
       </c>
@@ -10148,7 +10167,7 @@
       <c r="G113" s="1"/>
       <c r="H113" s="1"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>15.8</v>
       </c>
@@ -10165,7 +10184,7 @@
       <c r="G114" s="1"/>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>16.2</v>
       </c>
@@ -10182,7 +10201,7 @@
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>16.5</v>
       </c>
@@ -10199,7 +10218,7 @@
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>16.899999999999999</v>
       </c>
@@ -10216,7 +10235,7 @@
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>17.399999999999999</v>
       </c>
@@ -10233,7 +10252,7 @@
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>18.2</v>
       </c>
@@ -10250,7 +10269,7 @@
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>19.600000000000001</v>
       </c>
@@ -10267,7 +10286,7 @@
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>20</v>
       </c>
@@ -10284,7 +10303,7 @@
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>20.5</v>
       </c>
@@ -10301,7 +10320,7 @@
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>21</v>
       </c>
@@ -10318,7 +10337,7 @@
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>21.5</v>
       </c>
@@ -10335,7 +10354,7 @@
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>22.1</v>
       </c>
@@ -10352,7 +10371,7 @@
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>22.6</v>
       </c>
@@ -10369,7 +10388,7 @@
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>23.2</v>
       </c>
@@ -10386,7 +10405,7 @@
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>23.7</v>
       </c>
@@ -10403,7 +10422,7 @@
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>24.3</v>
       </c>
@@ -10420,7 +10439,7 @@
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>24.9</v>
       </c>
@@ -10437,7 +10456,7 @@
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>25.5</v>
       </c>
@@ -10454,7 +10473,7 @@
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>26.1</v>
       </c>
@@ -10471,7 +10490,7 @@
       <c r="G132" s="1"/>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>26.7</v>
       </c>
@@ -10488,7 +10507,7 @@
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>27.4</v>
       </c>
@@ -10505,7 +10524,7 @@
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>28</v>
       </c>
@@ -10522,7 +10541,7 @@
       <c r="G135" s="1"/>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>28.7</v>
       </c>
@@ -10539,7 +10558,7 @@
       <c r="G136" s="1"/>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>29.4</v>
       </c>
@@ -10556,7 +10575,7 @@
       <c r="G137" s="1"/>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>30.1</v>
       </c>
@@ -10573,7 +10592,7 @@
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>30.9</v>
       </c>
@@ -10590,7 +10609,7 @@
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>31.6</v>
       </c>
@@ -10607,7 +10626,7 @@
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>32.4</v>
       </c>
@@ -10624,7 +10643,7 @@
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>33.200000000000003</v>
       </c>
@@ -10641,7 +10660,7 @@
       <c r="G142" s="1"/>
       <c r="H142" s="1"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>34</v>
       </c>
@@ -10658,7 +10677,7 @@
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>34.799999999999997</v>
       </c>
@@ -10675,7 +10694,7 @@
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>35.700000000000003</v>
       </c>
@@ -10692,7 +10711,7 @@
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>36.5</v>
       </c>
@@ -10709,7 +10728,7 @@
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>37.4</v>
       </c>
@@ -10726,7 +10745,7 @@
       <c r="G147" s="1"/>
       <c r="H147" s="1"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>38.299999999999997</v>
       </c>
@@ -10743,7 +10762,7 @@
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>39.200000000000003</v>
       </c>
@@ -10760,7 +10779,7 @@
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>40.200000000000003</v>
       </c>
@@ -10777,7 +10796,7 @@
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>41.2</v>
       </c>
@@ -10794,7 +10813,7 @@
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>42.4</v>
       </c>
@@ -10811,7 +10830,7 @@
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>43.2</v>
       </c>
@@ -10828,7 +10847,7 @@
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>44.2</v>
       </c>
@@ -10845,7 +10864,7 @@
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>45.2</v>
       </c>
@@ -10862,7 +10881,7 @@
       <c r="G155" s="1"/>
       <c r="H155" s="1"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>46.4</v>
       </c>
@@ -10879,7 +10898,7 @@
       <c r="G156" s="1"/>
       <c r="H156" s="1"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>47.5</v>
       </c>
@@ -10896,7 +10915,7 @@
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>48.7</v>
       </c>
@@ -10913,7 +10932,7 @@
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>49.9</v>
       </c>
@@ -10930,7 +10949,7 @@
       <c r="G159" s="1"/>
       <c r="H159" s="1"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>51.1</v>
       </c>
@@ -10947,7 +10966,7 @@
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>52.3</v>
       </c>
@@ -10964,7 +10983,7 @@
       <c r="G161" s="1"/>
       <c r="H161" s="1"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>53.6</v>
       </c>
@@ -10981,7 +11000,7 @@
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>54.9</v>
       </c>
@@ -10998,7 +11017,7 @@
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>56.2</v>
       </c>
@@ -11015,7 +11034,7 @@
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>57.6</v>
       </c>
@@ -11032,7 +11051,7 @@
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>59</v>
       </c>
@@ -11049,7 +11068,7 @@
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>60.4</v>
       </c>
@@ -11066,7 +11085,7 @@
       <c r="G167" s="1"/>
       <c r="H167" s="1"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>61.9</v>
       </c>
@@ -11083,7 +11102,7 @@
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>63.4</v>
       </c>
@@ -11100,7 +11119,7 @@
       <c r="G169" s="1"/>
       <c r="H169" s="1"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>64.900000000000006</v>
       </c>
@@ -11108,7 +11127,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>66.5</v>
       </c>
@@ -11116,7 +11135,7 @@
         <v>147000</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>68.099999999999994</v>
       </c>
@@ -11124,7 +11143,7 @@
         <v>143000</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>69.8</v>
       </c>
@@ -11132,7 +11151,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>71.5</v>
       </c>
@@ -11140,7 +11159,7 @@
         <v>137000</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>73.2</v>
       </c>
@@ -11148,7 +11167,7 @@
         <v>133000</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>75</v>
       </c>
@@ -11156,7 +11175,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>76.8</v>
       </c>
@@ -11164,7 +11183,7 @@
         <v>127000</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>78.7</v>
       </c>
@@ -11172,7 +11191,7 @@
         <v>124000</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>80.599999999999994</v>
       </c>
@@ -11180,7 +11199,7 @@
         <v>121000</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>82.5</v>
       </c>
@@ -11188,7 +11207,7 @@
         <v>118000</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>84.5</v>
       </c>
@@ -11196,7 +11215,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>86.6</v>
       </c>
@@ -11204,7 +11223,7 @@
         <v>113000</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>88.7</v>
       </c>
@@ -11212,7 +11231,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>90.9</v>
       </c>
@@ -11220,7 +11239,7 @@
         <v>107000</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>93.1</v>
       </c>
@@ -11228,7 +11247,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>95.3</v>
       </c>
@@ -11236,7 +11255,7 @@
         <v>102000</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>97.6</v>
       </c>
@@ -11244,7 +11263,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>100</v>
       </c>
@@ -11252,7 +11271,7 @@
         <v>97600</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>102</v>
       </c>
@@ -11260,7 +11279,7 @@
         <v>95300</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>105</v>
       </c>
@@ -11268,7 +11287,7 @@
         <v>93100</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>107</v>
       </c>
@@ -11276,7 +11295,7 @@
         <v>90900</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>110</v>
       </c>
@@ -11284,7 +11303,7 @@
         <v>88700</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>113</v>
       </c>
@@ -11292,7 +11311,7 @@
         <v>86600</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>115</v>
       </c>
@@ -11300,7 +11319,7 @@
         <v>84500</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>118</v>
       </c>
@@ -11308,7 +11327,7 @@
         <v>82500</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>121</v>
       </c>
@@ -11316,7 +11335,7 @@
         <v>80600</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>124</v>
       </c>
@@ -11324,7 +11343,7 @@
         <v>78700</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>127</v>
       </c>
@@ -11332,7 +11351,7 @@
         <v>76800</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>130</v>
       </c>
@@ -11340,7 +11359,7 @@
         <v>75000</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>133</v>
       </c>
@@ -11348,7 +11367,7 @@
         <v>73200</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>137</v>
       </c>
@@ -11356,7 +11375,7 @@
         <v>71500</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>140</v>
       </c>
@@ -11364,7 +11383,7 @@
         <v>69800</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>143</v>
       </c>
@@ -11372,7 +11391,7 @@
         <v>68100</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>147</v>
       </c>
@@ -11380,7 +11399,7 @@
         <v>66500</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>150</v>
       </c>
@@ -11388,7 +11407,7 @@
         <v>64900</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>154</v>
       </c>
@@ -11396,7 +11415,7 @@
         <v>63400</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>158</v>
       </c>
@@ -11404,7 +11423,7 @@
         <v>61900</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>162</v>
       </c>
@@ -11412,7 +11431,7 @@
         <v>60400</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>165</v>
       </c>
@@ -11420,7 +11439,7 @@
         <v>59000</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>169</v>
       </c>
@@ -11428,7 +11447,7 @@
         <v>57600</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>174</v>
       </c>
@@ -11436,7 +11455,7 @@
         <v>56200</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>182</v>
       </c>
@@ -11444,7 +11463,7 @@
         <v>54900</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>196</v>
       </c>
@@ -11452,7 +11471,7 @@
         <v>53600</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>200</v>
       </c>
@@ -11460,7 +11479,7 @@
         <v>52300</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>205</v>
       </c>
@@ -11468,7 +11487,7 @@
         <v>51100</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>210</v>
       </c>
@@ -11476,7 +11495,7 @@
         <v>49900</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>215</v>
       </c>
@@ -11484,7 +11503,7 @@
         <v>48700</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>221</v>
       </c>
@@ -11492,7 +11511,7 @@
         <v>47500</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>226</v>
       </c>
@@ -11500,7 +11519,7 @@
         <v>46400</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>232</v>
       </c>
@@ -11508,7 +11527,7 @@
         <v>45200</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>237</v>
       </c>
@@ -11516,7 +11535,7 @@
         <v>44200</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>243</v>
       </c>
@@ -11524,7 +11543,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>249</v>
       </c>
@@ -11532,7 +11551,7 @@
         <v>42400</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>255</v>
       </c>
@@ -11540,7 +11559,7 @@
         <v>41200</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>261</v>
       </c>
@@ -11548,7 +11567,7 @@
         <v>40200</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>267</v>
       </c>
@@ -11556,7 +11575,7 @@
         <v>39200</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>274</v>
       </c>
@@ -11564,7 +11583,7 @@
         <v>38300</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>280</v>
       </c>
@@ -11572,7 +11591,7 @@
         <v>37400</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>287</v>
       </c>
@@ -11580,7 +11599,7 @@
         <v>36500</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>294</v>
       </c>
@@ -11588,7 +11607,7 @@
         <v>35700</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>301</v>
       </c>
@@ -11596,7 +11615,7 @@
         <v>34800</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>309</v>
       </c>
@@ -11604,7 +11623,7 @@
         <v>34000</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>316</v>
       </c>
@@ -11612,7 +11631,7 @@
         <v>33200</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>324</v>
       </c>
@@ -11620,7 +11639,7 @@
         <v>32400</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>332</v>
       </c>
@@ -11628,7 +11647,7 @@
         <v>31600</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>340</v>
       </c>
@@ -11636,7 +11655,7 @@
         <v>30900</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>348</v>
       </c>
@@ -11644,7 +11663,7 @@
         <v>30100</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>357</v>
       </c>
@@ -11652,7 +11671,7 @@
         <v>29400</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>365</v>
       </c>
@@ -11660,7 +11679,7 @@
         <v>28700</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>374</v>
       </c>
@@ -11668,7 +11687,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>383</v>
       </c>
@@ -11676,7 +11695,7 @@
         <v>27400</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>392</v>
       </c>
@@ -11684,7 +11703,7 @@
         <v>26700</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>402</v>
       </c>
@@ -11692,7 +11711,7 @@
         <v>26100</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>412</v>
       </c>
@@ -11700,7 +11719,7 @@
         <v>25500</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>424</v>
       </c>
@@ -11708,7 +11727,7 @@
         <v>24900</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>432</v>
       </c>
@@ -11716,7 +11735,7 @@
         <v>24300</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>442</v>
       </c>
@@ -11724,7 +11743,7 @@
         <v>23700</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>452</v>
       </c>
@@ -11732,7 +11751,7 @@
         <v>23200</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>464</v>
       </c>
@@ -11740,7 +11759,7 @@
         <v>22600</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>475</v>
       </c>
@@ -11748,7 +11767,7 @@
         <v>22100</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>487</v>
       </c>
@@ -11756,7 +11775,7 @@
         <v>21500</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>499</v>
       </c>
@@ -11764,7 +11783,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>511</v>
       </c>
@@ -11772,7 +11791,7 @@
         <v>20500</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>523</v>
       </c>
@@ -11780,7 +11799,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>536</v>
       </c>
@@ -11788,7 +11807,7 @@
         <v>19600</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>549</v>
       </c>
@@ -11796,7 +11815,7 @@
         <v>18200</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>562</v>
       </c>
@@ -11804,7 +11823,7 @@
         <v>17400</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>576</v>
       </c>
@@ -11812,7 +11831,7 @@
         <v>16900</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>590</v>
       </c>
@@ -11820,7 +11839,7 @@
         <v>16500</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>604</v>
       </c>
@@ -11828,7 +11847,7 @@
         <v>16200</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>619</v>
       </c>
@@ -11836,7 +11855,7 @@
         <v>15800</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>634</v>
       </c>
@@ -11844,7 +11863,7 @@
         <v>15400</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>649</v>
       </c>
@@ -11852,7 +11871,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>665</v>
       </c>
@@ -11860,7 +11879,7 @@
         <v>14700</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>681</v>
       </c>
@@ -11868,7 +11887,7 @@
         <v>14300</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>698</v>
       </c>
@@ -11876,7 +11895,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>715</v>
       </c>
@@ -11884,7 +11903,7 @@
         <v>13700</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>732</v>
       </c>
@@ -11892,7 +11911,7 @@
         <v>13300</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>750</v>
       </c>
@@ -11900,7 +11919,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>768</v>
       </c>
@@ -11908,7 +11927,7 @@
         <v>12700</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>787</v>
       </c>
@@ -11916,7 +11935,7 @@
         <v>12400</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>806</v>
       </c>
@@ -11924,7 +11943,7 @@
         <v>12100</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>825</v>
       </c>
@@ -11932,7 +11951,7 @@
         <v>11800</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>845</v>
       </c>
@@ -11940,7 +11959,7 @@
         <v>11500</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>866</v>
       </c>
@@ -11948,7 +11967,7 @@
         <v>11300</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>887</v>
       </c>
@@ -11956,7 +11975,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>909</v>
       </c>
@@ -11964,7 +11983,7 @@
         <v>10700</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>931</v>
       </c>
@@ -11972,7 +11991,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>953</v>
       </c>
@@ -11980,7 +11999,7 @@
         <v>10200</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>976</v>
       </c>
@@ -11988,7 +12007,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>1000</v>
       </c>
@@ -11996,7 +12015,7 @@
         <v>9760</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>1020</v>
       </c>
@@ -12004,7 +12023,7 @@
         <v>9530</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>1050</v>
       </c>
@@ -12012,7 +12031,7 @@
         <v>9310</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>1070</v>
       </c>
@@ -12020,7 +12039,7 @@
         <v>9090</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>1100</v>
       </c>
@@ -12028,7 +12047,7 @@
         <v>8870</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>1130</v>
       </c>
@@ -12036,7 +12055,7 @@
         <v>8660</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>1150</v>
       </c>
@@ -12044,7 +12063,7 @@
         <v>8450</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>1180</v>
       </c>
@@ -12052,7 +12071,7 @@
         <v>8250</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>1210</v>
       </c>
@@ -12060,7 +12079,7 @@
         <v>8060</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>1240</v>
       </c>
@@ -12068,7 +12087,7 @@
         <v>7870</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>1270</v>
       </c>
@@ -12076,7 +12095,7 @@
         <v>7680</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>1300</v>
       </c>
@@ -12084,7 +12103,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>1330</v>
       </c>
@@ -12092,7 +12111,7 @@
         <v>7320</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>1370</v>
       </c>
@@ -12100,7 +12119,7 @@
         <v>7150</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>1400</v>
       </c>
@@ -12108,7 +12127,7 @@
         <v>6980</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>1430</v>
       </c>
@@ -12116,7 +12135,7 @@
         <v>6810</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>1470</v>
       </c>
@@ -12124,7 +12143,7 @@
         <v>6650</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>1500</v>
       </c>
@@ -12132,7 +12151,7 @@
         <v>6490</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>1540</v>
       </c>
@@ -12140,7 +12159,7 @@
         <v>6340</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>1580</v>
       </c>
@@ -12148,7 +12167,7 @@
         <v>6190</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>1620</v>
       </c>
@@ -12156,7 +12175,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>1650</v>
       </c>
@@ -12164,7 +12183,7 @@
         <v>5900</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>1690</v>
       </c>
@@ -12172,7 +12191,7 @@
         <v>5760</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>1740</v>
       </c>
@@ -12180,7 +12199,7 @@
         <v>5620</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>1820</v>
       </c>
@@ -12188,7 +12207,7 @@
         <v>5490</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>1960</v>
       </c>
@@ -12196,7 +12215,7 @@
         <v>5360</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>2000</v>
       </c>
@@ -12204,7 +12223,7 @@
         <v>5230</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>2050</v>
       </c>
@@ -12212,7 +12231,7 @@
         <v>5110</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>2100</v>
       </c>
@@ -12220,7 +12239,7 @@
         <v>4990</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>2150</v>
       </c>
@@ -12228,7 +12247,7 @@
         <v>4870</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>2210</v>
       </c>
@@ -12236,7 +12255,7 @@
         <v>4750</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>2260</v>
       </c>
@@ -12244,7 +12263,7 @@
         <v>4640</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>2320</v>
       </c>
@@ -12252,7 +12271,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
         <v>2370</v>
       </c>
@@ -12260,7 +12279,7 @@
         <v>4420</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
         <v>2430</v>
       </c>
@@ -12268,7 +12287,7 @@
         <v>4320</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>2490</v>
       </c>
@@ -12276,7 +12295,7 @@
         <v>4240</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>2550</v>
       </c>
@@ -12284,7 +12303,7 @@
         <v>4120</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>2610</v>
       </c>
@@ -12292,7 +12311,7 @@
         <v>4020</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>2670</v>
       </c>
@@ -12300,7 +12319,7 @@
         <v>3920</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>2740</v>
       </c>
@@ -12308,7 +12327,7 @@
         <v>3830</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>2800</v>
       </c>
@@ -12316,7 +12335,7 @@
         <v>3740</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>2870</v>
       </c>
@@ -12324,7 +12343,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>2940</v>
       </c>
@@ -12332,7 +12351,7 @@
         <v>3570</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>3010</v>
       </c>
@@ -12340,7 +12359,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>3090</v>
       </c>
@@ -12348,7 +12367,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>3160</v>
       </c>
@@ -12356,7 +12375,7 @@
         <v>3320</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>3240</v>
       </c>
@@ -12364,7 +12383,7 @@
         <v>3240</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>3320</v>
       </c>
@@ -12372,7 +12391,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>3400</v>
       </c>
@@ -12380,7 +12399,7 @@
         <v>3090</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>3480</v>
       </c>
@@ -12388,7 +12407,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>3570</v>
       </c>
@@ -12396,7 +12415,7 @@
         <v>2940</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>3650</v>
       </c>
@@ -12404,7 +12423,7 @@
         <v>2870</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>3740</v>
       </c>
@@ -12412,7 +12431,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>3830</v>
       </c>
@@ -12420,7 +12439,7 @@
         <v>2740</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>3920</v>
       </c>
@@ -12428,7 +12447,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>4020</v>
       </c>
@@ -12436,7 +12455,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>4120</v>
       </c>
@@ -12444,7 +12463,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>4240</v>
       </c>
@@ -12452,7 +12471,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>4320</v>
       </c>
@@ -12460,7 +12479,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>4420</v>
       </c>
@@ -12468,7 +12487,7 @@
         <v>2370</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>4520</v>
       </c>
@@ -12476,7 +12495,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>4640</v>
       </c>
@@ -12484,7 +12503,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>4750</v>
       </c>
@@ -12492,7 +12511,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>4870</v>
       </c>
@@ -12500,7 +12519,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>4990</v>
       </c>
@@ -12508,7 +12527,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>5110</v>
       </c>
@@ -12516,7 +12535,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>5230</v>
       </c>
@@ -12524,7 +12543,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>5360</v>
       </c>
@@ -12532,7 +12551,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>5490</v>
       </c>
@@ -12540,7 +12559,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>5620</v>
       </c>
@@ -12548,7 +12567,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>5760</v>
       </c>
@@ -12556,7 +12575,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>5900</v>
       </c>
@@ -12564,7 +12583,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>6040</v>
       </c>
@@ -12572,7 +12591,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>6190</v>
       </c>
@@ -12580,7 +12599,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>6340</v>
       </c>
@@ -12588,7 +12607,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>6490</v>
       </c>
@@ -12596,7 +12615,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>6650</v>
       </c>
@@ -12604,7 +12623,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>6810</v>
       </c>
@@ -12612,7 +12631,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>6980</v>
       </c>
@@ -12620,7 +12639,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>7150</v>
       </c>
@@ -12628,7 +12647,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>7320</v>
       </c>
@@ -12636,7 +12655,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>7500</v>
       </c>
@@ -12644,7 +12663,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>7680</v>
       </c>
@@ -12652,7 +12671,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>7870</v>
       </c>
@@ -12660,7 +12679,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>8060</v>
       </c>
@@ -12668,7 +12687,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>8250</v>
       </c>
@@ -12676,7 +12695,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>8450</v>
       </c>
@@ -12684,7 +12703,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>8660</v>
       </c>
@@ -12692,7 +12711,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>8870</v>
       </c>
@@ -12700,7 +12719,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>9090</v>
       </c>
@@ -12708,7 +12727,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>9310</v>
       </c>
@@ -12716,7 +12735,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>9530</v>
       </c>
@@ -12724,7 +12743,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>9760</v>
       </c>
@@ -12732,7 +12751,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>10000</v>
       </c>
@@ -12740,7 +12759,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>10200</v>
       </c>
@@ -12748,7 +12767,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>10500</v>
       </c>
@@ -12756,7 +12775,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>10700</v>
       </c>
@@ -12764,7 +12783,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>11000</v>
       </c>
@@ -12772,7 +12791,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>11300</v>
       </c>
@@ -12780,7 +12799,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>11500</v>
       </c>
@@ -12788,7 +12807,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>11800</v>
       </c>
@@ -12796,7 +12815,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>12100</v>
       </c>
@@ -12804,7 +12823,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>12400</v>
       </c>
@@ -12812,7 +12831,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>12700</v>
       </c>
@@ -12820,7 +12839,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>13000</v>
       </c>
@@ -12828,7 +12847,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>13300</v>
       </c>
@@ -12836,7 +12855,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>13700</v>
       </c>
@@ -12844,7 +12863,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>14000</v>
       </c>
@@ -12852,7 +12871,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>14300</v>
       </c>
@@ -12860,7 +12879,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>14700</v>
       </c>
@@ -12868,7 +12887,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>15000</v>
       </c>
@@ -12876,7 +12895,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>15400</v>
       </c>
@@ -12884,7 +12903,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>15800</v>
       </c>
@@ -12892,7 +12911,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>16200</v>
       </c>
@@ -12900,7 +12919,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>16500</v>
       </c>
@@ -12908,7 +12927,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>16900</v>
       </c>
@@ -12916,7 +12935,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>17400</v>
       </c>
@@ -12924,7 +12943,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>18200</v>
       </c>
@@ -12932,7 +12951,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>19600</v>
       </c>
@@ -12940,7 +12959,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>20000</v>
       </c>
@@ -12948,7 +12967,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>20500</v>
       </c>
@@ -12956,7 +12975,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>21000</v>
       </c>
@@ -12964,7 +12983,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>21500</v>
       </c>
@@ -12972,7 +12991,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>22100</v>
       </c>
@@ -12980,7 +12999,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>22600</v>
       </c>
@@ -12988,7 +13007,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>23200</v>
       </c>
@@ -12996,7 +13015,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>23700</v>
       </c>
@@ -13004,7 +13023,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>24300</v>
       </c>
@@ -13012,7 +13031,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>24900</v>
       </c>
@@ -13020,7 +13039,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>25500</v>
       </c>
@@ -13028,7 +13047,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>26100</v>
       </c>
@@ -13036,7 +13055,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>26700</v>
       </c>
@@ -13044,7 +13063,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>27400</v>
       </c>
@@ -13052,7 +13071,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>28000</v>
       </c>
@@ -13060,7 +13079,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>28700</v>
       </c>
@@ -13068,7 +13087,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>29400</v>
       </c>
@@ -13076,7 +13095,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>30100</v>
       </c>
@@ -13084,7 +13103,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>30900</v>
       </c>
@@ -13092,7 +13111,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>31600</v>
       </c>
@@ -13100,7 +13119,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>32400</v>
       </c>
@@ -13108,7 +13127,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>33200</v>
       </c>
@@ -13116,7 +13135,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>34000</v>
       </c>
@@ -13124,7 +13143,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>34800</v>
       </c>
@@ -13132,7 +13151,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>35700</v>
       </c>
@@ -13140,7 +13159,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>36500</v>
       </c>
@@ -13148,7 +13167,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>37400</v>
       </c>
@@ -13156,7 +13175,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>38300</v>
       </c>
@@ -13164,7 +13183,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>39200</v>
       </c>
@@ -13172,7 +13191,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>40200</v>
       </c>
@@ -13180,7 +13199,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>41200</v>
       </c>
@@ -13188,7 +13207,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>42400</v>
       </c>
@@ -13196,7 +13215,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>43200</v>
       </c>
@@ -13204,7 +13223,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>44200</v>
       </c>
@@ -13212,7 +13231,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>45200</v>
       </c>
@@ -13220,7 +13239,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>46400</v>
       </c>
@@ -13228,7 +13247,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>47500</v>
       </c>
@@ -13236,7 +13255,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>48700</v>
       </c>
@@ -13244,7 +13263,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>49900</v>
       </c>
@@ -13252,7 +13271,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>51100</v>
       </c>
@@ -13260,7 +13279,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>52300</v>
       </c>
@@ -13268,7 +13287,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>53600</v>
       </c>
@@ -13276,7 +13295,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>54900</v>
       </c>
@@ -13284,7 +13303,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>56200</v>
       </c>
@@ -13292,7 +13311,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>57600</v>
       </c>
@@ -13300,7 +13319,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>59000</v>
       </c>
@@ -13308,7 +13327,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>60400</v>
       </c>
@@ -13316,7 +13335,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>61900</v>
       </c>
@@ -13324,7 +13343,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>63400</v>
       </c>
@@ -13332,7 +13351,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>64900</v>
       </c>
@@ -13340,7 +13359,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>66500</v>
       </c>
@@ -13348,7 +13367,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>68100</v>
       </c>
@@ -13356,7 +13375,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>69800</v>
       </c>
@@ -13364,7 +13383,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>71500</v>
       </c>
@@ -13372,7 +13391,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>73200</v>
       </c>
@@ -13380,7 +13399,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>75000</v>
       </c>
@@ -13388,7 +13407,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>76800</v>
       </c>
@@ -13396,7 +13415,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>78700</v>
       </c>
@@ -13404,7 +13423,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>80600</v>
       </c>
@@ -13412,7 +13431,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>82500</v>
       </c>
@@ -13420,7 +13439,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>84500</v>
       </c>
@@ -13428,7 +13447,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>86600</v>
       </c>
@@ -13436,7 +13455,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>88700</v>
       </c>
@@ -13444,7 +13463,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>90900</v>
       </c>
@@ -13452,7 +13471,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>93100</v>
       </c>
@@ -13460,7 +13479,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>95300</v>
       </c>
@@ -13468,7 +13487,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>97600</v>
       </c>
@@ -13476,7 +13495,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A467" s="8">
         <v>100000</v>
       </c>
@@ -13484,7 +13503,7 @@
         <v>97.6</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A468" s="8">
         <v>102000</v>
       </c>
@@ -13492,7 +13511,7 @@
         <v>95.3</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A469" s="8">
         <v>105000</v>
       </c>
@@ -13500,7 +13519,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A470" s="8">
         <v>107000</v>
       </c>
@@ -13508,7 +13527,7 @@
         <v>90.9</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A471" s="8">
         <v>110000</v>
       </c>
@@ -13516,7 +13535,7 @@
         <v>88.7</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A472" s="8">
         <v>113000</v>
       </c>
@@ -13524,7 +13543,7 @@
         <v>86.6</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A473" s="8">
         <v>115000</v>
       </c>
@@ -13532,7 +13551,7 @@
         <v>84.5</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A474" s="8">
         <v>118000</v>
       </c>
@@ -13540,7 +13559,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A475" s="8">
         <v>121000</v>
       </c>
@@ -13548,7 +13567,7 @@
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A476" s="8">
         <v>124000</v>
       </c>
@@ -13556,7 +13575,7 @@
         <v>78.7</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A477" s="8">
         <v>127000</v>
       </c>
@@ -13564,7 +13583,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A478" s="8">
         <v>130000</v>
       </c>
@@ -13572,7 +13591,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A479" s="8">
         <v>133000</v>
       </c>
@@ -13580,7 +13599,7 @@
         <v>73.2</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A480" s="8">
         <v>137000</v>
       </c>
@@ -13588,7 +13607,7 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A481" s="8">
         <v>140000</v>
       </c>
@@ -13596,7 +13615,7 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A482" s="8">
         <v>143000</v>
       </c>
@@ -13604,7 +13623,7 @@
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A483" s="8">
         <v>147000</v>
       </c>
@@ -13612,7 +13631,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A484" s="8">
         <v>150000</v>
       </c>
@@ -13620,7 +13639,7 @@
         <v>64.900000000000006</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A485" s="8">
         <v>154000</v>
       </c>
@@ -13628,7 +13647,7 @@
         <v>63.4</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A486" s="8">
         <v>158000</v>
       </c>
@@ -13636,7 +13655,7 @@
         <v>61.9</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A487" s="8">
         <v>162000</v>
       </c>
@@ -13644,7 +13663,7 @@
         <v>60.4</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A488" s="8">
         <v>165000</v>
       </c>
@@ -13652,7 +13671,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A489" s="8">
         <v>169000</v>
       </c>
@@ -13660,7 +13679,7 @@
         <v>57.6</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A490" s="8">
         <v>174000</v>
       </c>
@@ -13668,7 +13687,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A491" s="8">
         <v>182000</v>
       </c>
@@ -13676,7 +13695,7 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A492" s="8">
         <v>196000</v>
       </c>
@@ -13684,7 +13703,7 @@
         <v>53.6</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A493" s="8">
         <v>200000</v>
       </c>
@@ -13692,7 +13711,7 @@
         <v>52.3</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A494" s="8">
         <v>205000</v>
       </c>
@@ -13700,7 +13719,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A495" s="8">
         <v>210000</v>
       </c>
@@ -13708,7 +13727,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A496" s="8">
         <v>215000</v>
       </c>
@@ -13716,7 +13735,7 @@
         <v>48.7</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A497" s="8">
         <v>221000</v>
       </c>
@@ -13724,7 +13743,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A498" s="8">
         <v>226000</v>
       </c>
@@ -13732,7 +13751,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A499" s="8">
         <v>232000</v>
       </c>
@@ -13740,7 +13759,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A500" s="8">
         <v>237000</v>
       </c>
@@ -13748,7 +13767,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A501" s="8">
         <v>243000</v>
       </c>
@@ -13756,7 +13775,7 @@
         <v>43.2</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A502" s="8">
         <v>249000</v>
       </c>
@@ -13764,7 +13783,7 @@
         <v>42.4</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A503" s="8">
         <v>255000</v>
       </c>
@@ -13772,7 +13791,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A504" s="8">
         <v>261000</v>
       </c>
@@ -13780,7 +13799,7 @@
         <v>40.200000000000003</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A505" s="8">
         <v>267000</v>
       </c>
@@ -13788,7 +13807,7 @@
         <v>39.200000000000003</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A506" s="8">
         <v>274000</v>
       </c>
@@ -13796,7 +13815,7 @@
         <v>38.299999999999997</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A507" s="8">
         <v>280000</v>
       </c>
@@ -13804,7 +13823,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A508" s="8">
         <v>287000</v>
       </c>
@@ -13812,7 +13831,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A509" s="8">
         <v>294000</v>
       </c>
@@ -13820,7 +13839,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A510" s="8">
         <v>301000</v>
       </c>
@@ -13828,7 +13847,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A511" s="8">
         <v>309000</v>
       </c>
@@ -13836,7 +13855,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A512" s="8">
         <v>316000</v>
       </c>
@@ -13844,7 +13863,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A513" s="8">
         <v>324000</v>
       </c>
@@ -13852,7 +13871,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A514" s="8">
         <v>332000</v>
       </c>
@@ -13860,7 +13879,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A515" s="8">
         <v>340000</v>
       </c>
@@ -13868,7 +13887,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A516" s="8">
         <v>348000</v>
       </c>
@@ -13876,7 +13895,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A517" s="8">
         <v>357000</v>
       </c>
@@ -13884,7 +13903,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A518" s="8">
         <v>365000</v>
       </c>
@@ -13892,7 +13911,7 @@
         <v>28.7</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A519" s="8">
         <v>374000</v>
       </c>
@@ -13900,7 +13919,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A520" s="8">
         <v>383000</v>
       </c>
@@ -13908,7 +13927,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A521" s="8">
         <v>392000</v>
       </c>
@@ -13916,7 +13935,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A522" s="8">
         <v>402000</v>
       </c>
@@ -13924,7 +13943,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A523" s="8">
         <v>412000</v>
       </c>
@@ -13932,7 +13951,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A524" s="8">
         <v>424000</v>
       </c>
@@ -13940,7 +13959,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A525" s="8">
         <v>432000</v>
       </c>
@@ -13948,7 +13967,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A526" s="8">
         <v>442000</v>
       </c>
@@ -13956,7 +13975,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A527" s="8">
         <v>452000</v>
       </c>
@@ -13964,7 +13983,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A528" s="8">
         <v>464000</v>
       </c>
@@ -13972,7 +13991,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A529" s="8">
         <v>475000</v>
       </c>
@@ -13980,7 +13999,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A530" s="8">
         <v>487000</v>
       </c>
@@ -13988,7 +14007,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A531" s="8">
         <v>499000</v>
       </c>
@@ -13996,7 +14015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A532" s="8">
         <v>511000</v>
       </c>
@@ -14004,7 +14023,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A533" s="8">
         <v>523000</v>
       </c>
@@ -14012,7 +14031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A534" s="8">
         <v>536000</v>
       </c>
@@ -14020,7 +14039,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A535" s="8">
         <v>549000</v>
       </c>
@@ -14028,7 +14047,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A536" s="8">
         <v>562000</v>
       </c>
@@ -14036,7 +14055,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A537" s="8">
         <v>576000</v>
       </c>
@@ -14044,7 +14063,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A538" s="8">
         <v>590000</v>
       </c>
@@ -14052,7 +14071,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A539" s="8">
         <v>604000</v>
       </c>
@@ -14060,7 +14079,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A540" s="8">
         <v>619000</v>
       </c>
@@ -14068,7 +14087,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A541" s="8">
         <v>634000</v>
       </c>
@@ -14076,7 +14095,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A542" s="8">
         <v>649000</v>
       </c>
@@ -14084,7 +14103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A543" s="8">
         <v>665000</v>
       </c>
@@ -14092,7 +14111,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A544" s="8">
         <v>681000</v>
       </c>
@@ -14100,7 +14119,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A545" s="8">
         <v>698000</v>
       </c>
@@ -14108,7 +14127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A546" s="8">
         <v>715000</v>
       </c>
@@ -14116,7 +14135,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A547" s="8">
         <v>732000</v>
       </c>
@@ -14124,7 +14143,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A548" s="8">
         <v>750000</v>
       </c>
@@ -14132,7 +14151,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A549" s="8">
         <v>768000</v>
       </c>
@@ -14140,7 +14159,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A550" s="8">
         <v>787000</v>
       </c>
@@ -14148,7 +14167,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A551" s="8">
         <v>806000</v>
       </c>
@@ -14156,7 +14175,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A552" s="8">
         <v>825000</v>
       </c>
@@ -14164,7 +14183,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A553" s="8">
         <v>845000</v>
       </c>
@@ -14172,7 +14191,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A554" s="8">
         <v>866000</v>
       </c>
@@ -14180,7 +14199,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A555" s="8">
         <v>887000</v>
       </c>
@@ -14188,7 +14207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A556" s="8">
         <v>909000</v>
       </c>
@@ -14196,7 +14215,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A557" s="8">
         <v>931000</v>
       </c>
@@ -14204,7 +14223,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A558" s="8">
         <v>953000</v>
       </c>
@@ -14212,7 +14231,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A559" s="8">
         <v>976000</v>
       </c>
@@ -14220,7 +14239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A560" s="8">
         <v>1000000</v>
       </c>
@@ -14228,7 +14247,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A561" s="8">
         <v>1020000</v>
       </c>
@@ -14236,7 +14255,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A562" s="8">
         <v>1050000</v>
       </c>
@@ -14244,7 +14263,7 @@
         <v>9.3099999999999987</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A563" s="8">
         <v>1070000</v>
       </c>
@@ -14252,7 +14271,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A564" s="8">
         <v>1100000</v>
       </c>
@@ -14260,7 +14279,7 @@
         <v>8.870000000000001</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A565" s="8">
         <v>1130000</v>
       </c>
@@ -14268,7 +14287,7 @@
         <v>8.66</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A566" s="8">
         <v>1150000</v>
       </c>
@@ -14276,7 +14295,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A567" s="8">
         <v>1180000</v>
       </c>
@@ -14284,7 +14303,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A568" s="8">
         <v>1210000</v>
       </c>
@@ -14292,7 +14311,7 @@
         <v>8.0599999999999987</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A569" s="8">
         <v>1240000</v>
       </c>
@@ -14300,7 +14319,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A570" s="8">
         <v>1270000</v>
       </c>
@@ -14308,7 +14327,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A571" s="8">
         <v>1300000</v>
       </c>
@@ -14316,7 +14335,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A572" s="8">
         <v>1330000</v>
       </c>
@@ -14324,7 +14343,7 @@
         <v>7.32</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A573" s="8">
         <v>1370000</v>
       </c>
@@ -14332,7 +14351,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A574" s="8">
         <v>1400000</v>
       </c>
@@ -14340,7 +14359,7 @@
         <v>6.9799999999999995</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A575" s="8">
         <v>1430000</v>
       </c>
@@ -14348,7 +14367,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A576" s="8">
         <v>1470000</v>
       </c>
@@ -14356,7 +14375,7 @@
         <v>6.65</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A577" s="8">
         <v>1500000</v>
       </c>
@@ -14364,7 +14383,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A578" s="8">
         <v>1540000</v>
       </c>
@@ -14372,7 +14391,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A579" s="8">
         <v>1580000</v>
       </c>
@@ -14380,7 +14399,7 @@
         <v>6.1899999999999995</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A580" s="8">
         <v>1620000</v>
       </c>
@@ -14388,7 +14407,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A581" s="8">
         <v>1650000</v>
       </c>
@@ -14396,7 +14415,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A582" s="8">
         <v>1690000</v>
       </c>
@@ -14404,7 +14423,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A583" s="8">
         <v>1740000</v>
       </c>
@@ -14412,7 +14431,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A584" s="8">
         <v>1820000</v>
       </c>
@@ -14420,7 +14439,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A585" s="8">
         <v>1960000</v>
       </c>
@@ -14428,7 +14447,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A586" s="8">
         <v>2000000</v>
       </c>
@@ -14436,7 +14455,7 @@
         <v>5.2299999999999995</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A587" s="8">
         <v>2050000</v>
       </c>
@@ -14444,7 +14463,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A588" s="8">
         <v>2100000</v>
       </c>
@@ -14452,7 +14471,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A589" s="8">
         <v>2150000</v>
       </c>
@@ -14460,7 +14479,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A590" s="8">
         <v>2210000</v>
       </c>
@@ -14468,7 +14487,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A591" s="8">
         <v>2260000</v>
       </c>
@@ -14476,7 +14495,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A592" s="8">
         <v>2320000</v>
       </c>
@@ -14484,7 +14503,7 @@
         <v>4.5200000000000005</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A593" s="8">
         <v>2370000</v>
       </c>
@@ -14492,7 +14511,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A594" s="8">
         <v>2430000</v>
       </c>
@@ -14500,7 +14519,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A595" s="8">
         <v>2490000</v>
       </c>
@@ -14508,7 +14527,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A596" s="8">
         <v>2550000</v>
       </c>
@@ -14516,7 +14535,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A597" s="8">
         <v>2610000</v>
       </c>
@@ -14524,7 +14543,7 @@
         <v>4.0200000000000005</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A598" s="8">
         <v>2670000</v>
       </c>
@@ -14532,7 +14551,7 @@
         <v>3.9200000000000004</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A599" s="8">
         <v>2740000</v>
       </c>
@@ -14540,7 +14559,7 @@
         <v>3.8299999999999996</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A600" s="8">
         <v>2800000</v>
       </c>
@@ -14548,7 +14567,7 @@
         <v>3.7399999999999998</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A601" s="8">
         <v>2870000</v>
       </c>
@@ -14556,7 +14575,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A602" s="8">
         <v>2940000</v>
       </c>
@@ -14564,7 +14583,7 @@
         <v>3.5700000000000003</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A603" s="8">
         <v>3010000</v>
       </c>
@@ -14572,7 +14591,7 @@
         <v>3.4799999999999995</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A604" s="8">
         <v>3090000</v>
       </c>
@@ -14580,7 +14599,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A605" s="8">
         <v>3160000</v>
       </c>
@@ -14588,7 +14607,7 @@
         <v>3.3200000000000003</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A606" s="8">
         <v>3240000</v>
       </c>
@@ -14596,7 +14615,7 @@
         <v>3.2399999999999998</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A607" s="8">
         <v>3320000</v>
       </c>
@@ -14604,7 +14623,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A608" s="8">
         <v>3400000</v>
       </c>
@@ -14612,7 +14631,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A609" s="8">
         <v>3480000</v>
       </c>
@@ -14620,7 +14639,7 @@
         <v>3.0100000000000002</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A610" s="8">
         <v>3570000</v>
       </c>
@@ -14628,7 +14647,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A611" s="8">
         <v>3650000</v>
       </c>
@@ -14636,7 +14655,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A612" s="8">
         <v>3740000</v>
       </c>
@@ -14644,7 +14663,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A613" s="8">
         <v>3830000</v>
       </c>
@@ -14652,7 +14671,7 @@
         <v>2.7399999999999998</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A614" s="8">
         <v>3920000</v>
       </c>
@@ -14660,7 +14679,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A615" s="8">
         <v>4020000</v>
       </c>
@@ -14668,7 +14687,7 @@
         <v>2.6100000000000003</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A616" s="8">
         <v>4120000</v>
       </c>
@@ -14676,7 +14695,7 @@
         <v>2.5499999999999998</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A617" s="8">
         <v>4240000</v>
       </c>
@@ -14684,7 +14703,7 @@
         <v>2.4899999999999998</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A618" s="8">
         <v>4320000</v>
       </c>
@@ -14692,7 +14711,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A619" s="8">
         <v>4420000</v>
       </c>
@@ -14700,7 +14719,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A620" s="8">
         <v>4520000</v>
       </c>
@@ -14708,7 +14727,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A621" s="8">
         <v>4640000</v>
       </c>
@@ -14716,7 +14735,7 @@
         <v>2.2600000000000002</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A622" s="8">
         <v>4750000</v>
       </c>
@@ -14724,7 +14743,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A623" s="8">
         <v>4870000</v>
       </c>
@@ -14732,7 +14751,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A624" s="8">
         <v>4990000</v>
       </c>
@@ -14740,7 +14759,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A625" s="8">
         <v>5110000</v>
       </c>
@@ -14748,7 +14767,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A626" s="8">
         <v>5230000</v>
       </c>
@@ -14756,7 +14775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A627" s="8">
         <v>5360000</v>
       </c>
@@ -14764,7 +14783,7 @@
         <v>1.9600000000000002</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A628" s="8">
         <v>5490000</v>
       </c>
@@ -14772,7 +14791,7 @@
         <v>1.8199999999999998</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A629" s="8">
         <v>5620000</v>
       </c>
@@ -14780,7 +14799,7 @@
         <v>1.7399999999999998</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A630" s="8">
         <v>5760000</v>
       </c>
@@ -14788,7 +14807,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A631" s="8">
         <v>5900000</v>
       </c>
@@ -14796,7 +14815,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A632" s="8">
         <v>6040000</v>
       </c>
@@ -14804,7 +14823,7 @@
         <v>1.6199999999999999</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A633" s="8">
         <v>6190000</v>
       </c>
@@ -14812,7 +14831,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A634" s="8">
         <v>6340000</v>
       </c>
@@ -14820,7 +14839,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A635" s="8">
         <v>6490000</v>
       </c>
@@ -14828,7 +14847,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A636" s="8">
         <v>6650000</v>
       </c>
@@ -14836,7 +14855,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A637" s="8">
         <v>6810000</v>
       </c>
@@ -14844,7 +14863,7 @@
         <v>1.4300000000000002</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A638" s="8">
         <v>6980000</v>
       </c>
@@ -14852,7 +14871,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A639" s="8">
         <v>7150000</v>
       </c>
@@ -14860,7 +14879,7 @@
         <v>1.3699999999999999</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A640" s="8">
         <v>7320000</v>
       </c>
@@ -14868,7 +14887,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A641" s="8">
         <v>7500000</v>
       </c>
@@ -14876,7 +14895,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A642" s="8">
         <v>7680000</v>
       </c>
@@ -14884,7 +14903,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A643" s="8">
         <v>7870000</v>
       </c>
@@ -14892,7 +14911,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A644" s="8">
         <v>8060000</v>
       </c>
@@ -14900,7 +14919,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A645" s="8">
         <v>8250000</v>
       </c>
@@ -14908,7 +14927,7 @@
         <v>1.1800000000000002</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A646" s="8">
         <v>8450000</v>
       </c>
@@ -14916,7 +14935,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A647" s="8">
         <v>8660000</v>
       </c>
@@ -14924,7 +14943,7 @@
         <v>1.1300000000000001</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A648" s="8">
         <v>8870000</v>
       </c>
@@ -14932,7 +14951,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A649" s="8">
         <v>9090000</v>
       </c>
@@ -14940,7 +14959,7 @@
         <v>1.0699999999999998</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A650" s="8">
         <v>9310000</v>
       </c>
@@ -14948,7 +14967,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A651" s="8">
         <v>9530000</v>
       </c>
@@ -14956,7 +14975,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A652" s="8">
         <v>9760000</v>
       </c>
@@ -14964,93 +14983,93 @@
         <v>1</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A653" s="1"/>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A654" s="1"/>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A655" s="1"/>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A656" s="1"/>
     </row>
-    <row r="657" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A657" s="1"/>
     </row>
-    <row r="658" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A658" s="1"/>
     </row>
-    <row r="659" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A659" s="1"/>
     </row>
-    <row r="660" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A660" s="1"/>
     </row>
-    <row r="661" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A661" s="1"/>
     </row>
-    <row r="662" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A662" s="1"/>
     </row>
-    <row r="663" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A663" s="1"/>
     </row>
-    <row r="664" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A664" s="1"/>
     </row>
-    <row r="665" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A665" s="1"/>
     </row>
-    <row r="666" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A666" s="1"/>
     </row>
-    <row r="667" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A667" s="1"/>
     </row>
-    <row r="668" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A668" s="1"/>
     </row>
-    <row r="669" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A669" s="1"/>
     </row>
-    <row r="670" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A670" s="1"/>
     </row>
-    <row r="671" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A671" s="1"/>
     </row>
-    <row r="672" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A672" s="1"/>
     </row>
-    <row r="673" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A673" s="1"/>
     </row>
-    <row r="674" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A674" s="1"/>
     </row>
-    <row r="675" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A675" s="1"/>
     </row>
-    <row r="676" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A676" s="1"/>
     </row>
-    <row r="677" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A677" s="1"/>
     </row>
-    <row r="678" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A678" s="1"/>
     </row>
-    <row r="679" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A679" s="1"/>
     </row>
-    <row r="680" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A680" s="1"/>
     </row>
   </sheetData>
   <sheetProtection password="DADE" sheet="1" objects="1" scenarios="1"/>
-  <sortState ref="E2:I169">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="E2:I169">
     <sortCondition descending="1" ref="I2:I169"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
